--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>509.4717834624431</v>
+        <v>509.4887561620271</v>
       </c>
       <c r="C2">
-        <v>355.3164277330868</v>
+        <v>353.9303626477427</v>
       </c>
       <c r="D2">
-        <v>304.4963268950578</v>
+        <v>303.7536157154792</v>
       </c>
       <c r="E2">
-        <v>280.0897893419755</v>
+        <v>279.9981710521446</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>598.9935381844242</v>
+        <v>598.9979570893939</v>
       </c>
       <c r="C3">
-        <v>419.0915150814818</v>
+        <v>417.4088435645943</v>
       </c>
       <c r="D3">
-        <v>357.3594592318457</v>
+        <v>356.4812944438565</v>
       </c>
       <c r="E3">
-        <v>331.5630083491056</v>
+        <v>331.4526009137757</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>572.7150082520693</v>
+        <v>572.7123584722456</v>
       </c>
       <c r="C4">
-        <v>402.0101658226636</v>
+        <v>400.4147067581463</v>
       </c>
       <c r="D4">
-        <v>343.8982688741974</v>
+        <v>343.0640566099692</v>
       </c>
       <c r="E4">
-        <v>319.5015104924415</v>
+        <v>319.3932982943067</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>393.8699112426607</v>
+        <v>393.8702128052146</v>
       </c>
       <c r="C5">
-        <v>276.3110768592336</v>
+        <v>275.1793079127632</v>
       </c>
       <c r="D5">
-        <v>232.8408550402497</v>
+        <v>232.2527119711928</v>
       </c>
       <c r="E5">
-        <v>218.7053349206821</v>
+        <v>218.6234732383012</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>350.8963840745715</v>
+        <v>350.8966700368074</v>
       </c>
       <c r="C6">
-        <v>244.5030475833582</v>
+        <v>243.4972799170334</v>
       </c>
       <c r="D6">
-        <v>207.1892605313775</v>
+        <v>206.6617573465856</v>
       </c>
       <c r="E6">
-        <v>191.9988340830891</v>
+        <v>191.9268153068482</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36.68411565055315</v>
+        <v>36.68417528303408</v>
       </c>
       <c r="C7">
-        <v>25.58486625401695</v>
+        <v>25.48040326891089</v>
       </c>
       <c r="D7">
-        <v>21.91596888786883</v>
+        <v>21.86073392208547</v>
       </c>
       <c r="E7">
-        <v>20.25307581277349</v>
+        <v>20.24592520763254</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1998.468025715313</v>
+        <v>1998.556466962729</v>
       </c>
       <c r="C8">
-        <v>1393.853412283299</v>
+        <v>1388.850870118269</v>
       </c>
       <c r="D8">
-        <v>1204.279024121445</v>
+        <v>1202.36199703184</v>
       </c>
       <c r="E8">
-        <v>1103.372767904274</v>
+        <v>1103.258556038939</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>502.3898030613827</v>
+        <v>502.3915682440407</v>
       </c>
       <c r="C9">
-        <v>351.7173266962727</v>
+        <v>350.2858790668134</v>
       </c>
       <c r="D9">
-        <v>299.734004508032</v>
+        <v>298.9858571844774</v>
       </c>
       <c r="E9">
-        <v>278.4070048960226</v>
+        <v>278.3119401800335</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>204.4680061353053</v>
+        <v>204.4666065543753</v>
       </c>
       <c r="C10">
-        <v>143.1438391229902</v>
+        <v>142.6204576841496</v>
       </c>
       <c r="D10">
-        <v>125.5911132001598</v>
+        <v>125.2883148209374</v>
       </c>
       <c r="E10">
-        <v>115.0712114082426</v>
+        <v>115.0340193806114</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37.68742058254948</v>
+        <v>37.72779727648657</v>
       </c>
       <c r="C11">
-        <v>25.06104686309148</v>
+        <v>24.96903025190405</v>
       </c>
       <c r="D11">
-        <v>21.70492669859174</v>
+        <v>21.65230108027522</v>
       </c>
       <c r="E11">
-        <v>21.43795693297778</v>
+        <v>21.43104032990557</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>87.08378576801532</v>
+        <v>87.08876235443314</v>
       </c>
       <c r="C12">
-        <v>64.70116160461083</v>
+        <v>64.47598655857492</v>
       </c>
       <c r="D12">
-        <v>56.9860457271884</v>
+        <v>56.84911427691045</v>
       </c>
       <c r="E12">
-        <v>51.66515459616286</v>
+        <v>51.64807541420919</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>114.5930839945039</v>
+        <v>114.5922965229201</v>
       </c>
       <c r="C13">
-        <v>79.59768252295345</v>
+        <v>79.29456472277703</v>
       </c>
       <c r="D13">
-        <v>70.57154994444538</v>
+        <v>70.40121887897011</v>
       </c>
       <c r="E13">
-        <v>65.44540971612228</v>
+        <v>65.42383515170467</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>393.8702128052146</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>275.1793079127632</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>232.2527119711928</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>218.6234732383012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1998.556466962729</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1388.850870118269</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1202.36199703184</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1103.258556038939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>204.4666065543753</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>142.6204576841496</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>125.2883148209374</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>115.0340193806114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37.72779727648657</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>24.96903025190405</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>21.65230108027522</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>21.43104032990557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>114.5922965229201</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>79.29456472277703</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>70.40121887897011</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>65.42383515170467</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
